--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32500,7 +32500,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -199,11 +199,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -276,11 +271,6 @@
           <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -353,11 +343,6 @@
           <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -430,11 +415,6 @@
           <t xml:space="preserve">20.04.26</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -507,11 +487,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -589,11 +564,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -666,11 +636,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -743,11 +708,6 @@
           <t xml:space="preserve">28.01.26</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -825,11 +785,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -907,11 +862,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -989,11 +939,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1066,11 +1011,6 @@
           <t xml:space="preserve">30.01.26</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1148,11 +1088,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1225,11 +1160,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1302,11 +1232,6 @@
           <t xml:space="preserve">20.02.26</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2636,11 +2561,6 @@
           <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2790,11 +2710,6 @@
           <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2867,11 +2782,6 @@
           <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4345,11 +4255,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4427,11 +4332,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4827,11 +4727,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4904,11 +4799,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4981,11 +4871,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5058,11 +4943,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5135,11 +5015,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5212,11 +5087,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5371,11 +5241,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5448,11 +5313,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5525,11 +5385,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5602,11 +5457,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5684,11 +5534,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5766,11 +5611,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5848,11 +5688,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6012,11 +5847,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6094,11 +5924,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6176,11 +6001,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6258,11 +6078,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6340,11 +6155,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6422,11 +6232,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6504,11 +6309,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6586,11 +6386,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6668,11 +6463,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6750,11 +6540,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6832,11 +6617,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6914,11 +6694,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6996,11 +6771,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7078,11 +6848,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7160,11 +6925,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7314,11 +7074,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7396,11 +7151,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7478,11 +7228,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7560,11 +7305,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10084,11 +9824,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10248,11 +9983,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10325,11 +10055,6 @@
           <t xml:space="preserve">25.06.26</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10715,11 +10440,6 @@
           <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10797,11 +10517,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11033,11 +10748,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11115,11 +10825,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11197,11 +10902,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11279,11 +10979,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11361,11 +11056,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11443,11 +11133,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11525,11 +11210,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11607,11 +11287,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11689,11 +11364,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11771,11 +11441,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11853,11 +11518,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11935,11 +11595,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12017,11 +11672,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12099,11 +11749,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12417,11 +12062,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12494,11 +12134,6 @@
           <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12730,11 +12365,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12812,11 +12442,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12894,11 +12519,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12971,11 +12591,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13299,11 +12914,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13381,11 +12991,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13709,11 +13314,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13955,11 +13555,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14084,11 +13679,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14131,11 +13721,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14178,11 +13763,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14225,11 +13805,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14272,11 +13847,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14319,11 +13889,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14366,11 +13931,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14413,11 +13973,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14460,11 +14015,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14507,11 +14057,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14554,11 +14099,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14601,11 +14141,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14648,11 +14183,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14695,11 +14225,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14742,11 +14267,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14789,11 +14309,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14836,11 +14351,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14883,11 +14393,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14930,11 +14435,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14977,11 +14477,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15024,11 +14519,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15071,11 +14561,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15118,11 +14603,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15165,11 +14645,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15212,11 +14687,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15259,11 +14729,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15306,11 +14771,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15353,11 +14813,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15400,11 +14855,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15447,11 +14897,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15494,11 +14939,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15541,11 +14981,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15588,11 +15023,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15635,11 +15065,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15682,11 +15107,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15729,11 +15149,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15776,11 +15191,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15823,11 +15233,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15870,11 +15275,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15917,11 +15317,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15964,11 +15359,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16011,11 +15401,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16058,11 +15443,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16105,11 +15485,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16152,11 +15527,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16199,11 +15569,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16246,11 +15611,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16293,11 +15653,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16340,11 +15695,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16387,11 +15737,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16434,11 +15779,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16481,11 +15821,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16528,11 +15863,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16575,11 +15905,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16622,11 +15947,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16669,11 +15989,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16716,11 +16031,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16763,11 +16073,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16810,11 +16115,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16857,11 +16157,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16904,11 +16199,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16951,11 +16241,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16998,11 +16283,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17045,11 +16325,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17092,11 +16367,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17139,11 +16409,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17186,11 +16451,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17233,11 +16493,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17280,11 +16535,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17327,11 +16577,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17374,11 +16619,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17421,11 +16661,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17468,11 +16703,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17515,11 +16745,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17562,11 +16787,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17609,11 +16829,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17656,11 +16871,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17703,11 +16913,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17750,11 +16955,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17797,11 +16997,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17844,11 +17039,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17891,11 +17081,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17938,11 +17123,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17985,11 +17165,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18032,11 +17207,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18079,11 +17249,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18126,11 +17291,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18173,11 +17333,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18220,11 +17375,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18267,11 +17417,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18314,11 +17459,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18361,11 +17501,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18408,11 +17543,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18455,11 +17585,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18502,11 +17627,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18549,11 +17669,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18596,11 +17711,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18643,11 +17753,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18690,11 +17795,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18737,11 +17837,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18784,11 +17879,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18831,11 +17921,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18878,11 +17963,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18925,11 +18005,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18972,11 +18047,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19019,11 +18089,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19066,11 +18131,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19113,11 +18173,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19160,11 +18215,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19207,11 +18257,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19254,11 +18299,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19301,11 +18341,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19348,11 +18383,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19395,11 +18425,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19442,11 +18467,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19489,11 +18509,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19536,11 +18551,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19583,11 +18593,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19630,11 +18635,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19677,11 +18677,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19724,11 +18719,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19771,11 +18761,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19818,11 +18803,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19865,11 +18845,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19912,11 +18887,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19959,11 +18929,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20006,11 +18971,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20053,11 +19013,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20100,11 +19055,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20147,11 +19097,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20194,11 +19139,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20241,11 +19181,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20288,11 +19223,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20335,11 +19265,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20382,11 +19307,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20429,11 +19349,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20476,11 +19391,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20523,11 +19433,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20570,11 +19475,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20617,11 +19517,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20664,11 +19559,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20711,11 +19601,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20758,11 +19643,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20805,11 +19685,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20852,11 +19727,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20899,11 +19769,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20946,11 +19811,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20993,11 +19853,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21040,11 +19895,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21087,11 +19937,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21134,11 +19979,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21181,11 +20021,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21228,11 +20063,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21275,11 +20105,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21322,11 +20147,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21369,11 +20189,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21416,11 +20231,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21463,11 +20273,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21510,11 +20315,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21557,11 +20357,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21604,11 +20399,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21651,11 +20441,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21698,11 +20483,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21745,11 +20525,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21792,11 +20567,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21839,11 +20609,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21886,11 +20651,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21933,11 +20693,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21980,11 +20735,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22027,11 +20777,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22074,11 +20819,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22121,11 +20861,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22168,11 +20903,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22215,11 +20945,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22262,11 +20987,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22309,11 +21029,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22356,11 +21071,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22403,11 +21113,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22450,11 +21155,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22497,11 +21197,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22544,11 +21239,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22591,11 +21281,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22638,11 +21323,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22685,11 +21365,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22732,11 +21407,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22779,11 +21449,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22826,11 +21491,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22873,11 +21533,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22920,11 +21575,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22967,11 +21617,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23014,11 +21659,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23061,11 +21701,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23108,11 +21743,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23155,11 +21785,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23202,11 +21827,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23249,11 +21869,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23296,11 +21911,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23343,11 +21953,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23390,11 +21995,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23437,11 +22037,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23484,11 +22079,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23531,11 +22121,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23578,11 +22163,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23625,11 +22205,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23672,11 +22247,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23719,11 +22289,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23766,11 +22331,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23813,11 +22373,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23860,11 +22415,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23907,11 +22457,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23954,11 +22499,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24001,11 +22541,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24048,11 +22583,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24095,11 +22625,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24142,11 +22667,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24189,11 +22709,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24236,11 +22751,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24283,11 +22793,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24330,11 +22835,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24377,11 +22877,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24424,11 +22919,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24471,11 +22961,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24518,11 +23003,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24565,11 +23045,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24612,11 +23087,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24659,11 +23129,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24706,11 +23171,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24753,11 +23213,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24800,11 +23255,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24847,11 +23297,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24894,11 +23339,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24941,11 +23381,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24988,11 +23423,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25035,11 +23465,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25082,11 +23507,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25129,11 +23549,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25176,11 +23591,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25223,11 +23633,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25270,11 +23675,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25317,11 +23717,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25364,11 +23759,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25411,11 +23801,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25458,11 +23843,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25505,11 +23885,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25552,11 +23927,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25599,11 +23969,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25646,11 +24011,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25693,11 +24053,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25740,11 +24095,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25787,11 +24137,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25834,11 +24179,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25881,11 +24221,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25928,11 +24263,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25975,11 +24305,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26022,11 +24347,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26069,11 +24389,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26116,11 +24431,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26163,11 +24473,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26210,11 +24515,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26257,11 +24557,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26304,11 +24599,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26351,11 +24641,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26398,11 +24683,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26445,11 +24725,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26492,11 +24767,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26539,11 +24809,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26586,11 +24851,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26633,11 +24893,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26680,11 +24935,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26727,11 +24977,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26774,11 +25019,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26821,11 +25061,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26868,11 +25103,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26915,11 +25145,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26962,11 +25187,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27009,11 +25229,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27056,11 +25271,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27103,11 +25313,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27150,11 +25355,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27197,11 +25397,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27244,11 +25439,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27291,11 +25481,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27338,11 +25523,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27385,11 +25565,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27432,11 +25607,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27479,11 +25649,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27526,11 +25691,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27573,11 +25733,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27620,11 +25775,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27667,11 +25817,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27714,11 +25859,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27761,11 +25901,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27808,11 +25943,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27855,11 +25985,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27902,11 +26027,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27949,11 +26069,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27996,11 +26111,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28043,11 +26153,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28090,11 +26195,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28137,11 +26237,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28184,11 +26279,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28231,11 +26321,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28278,11 +26363,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28325,11 +26405,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28372,11 +26447,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28419,11 +26489,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28466,11 +26531,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28513,11 +26573,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28560,11 +26615,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28607,11 +26657,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28654,11 +26699,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28701,11 +26741,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28748,11 +26783,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28795,11 +26825,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28842,11 +26867,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28889,11 +26909,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28936,11 +26951,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28983,11 +26993,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29030,11 +27035,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29077,11 +27077,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29124,11 +27119,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29171,11 +27161,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29218,11 +27203,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29265,11 +27245,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29312,11 +27287,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29359,11 +27329,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29406,11 +27371,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29453,11 +27413,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L504" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M504" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29500,11 +27455,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L505" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M505" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29547,11 +27497,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M506" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29592,11 +27537,6 @@
       <c r="J507" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L507" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -199,6 +199,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -271,6 +276,11 @@
           <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -343,6 +353,11 @@
           <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -415,6 +430,11 @@
           <t xml:space="preserve">20.04.26</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -487,6 +507,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -564,6 +589,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -636,6 +666,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -708,6 +743,11 @@
           <t xml:space="preserve">28.01.26</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -785,6 +825,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -862,6 +907,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -939,6 +989,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1011,6 +1066,11 @@
           <t xml:space="preserve">30.01.26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1088,6 +1148,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1160,6 +1225,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1232,6 +1302,11 @@
           <t xml:space="preserve">20.02.26</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2561,6 +2636,11 @@
           <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2710,6 +2790,11 @@
           <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2782,6 +2867,11 @@
           <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4255,6 +4345,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4332,6 +4427,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4727,6 +4827,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4799,6 +4904,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4871,6 +4981,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4943,6 +5058,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5015,6 +5135,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5087,6 +5212,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5241,6 +5371,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5313,6 +5448,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5385,6 +5525,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5457,6 +5602,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5534,6 +5684,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5611,6 +5766,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5688,6 +5848,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5847,6 +6012,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5924,6 +6094,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6001,6 +6176,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6078,6 +6258,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6155,6 +6340,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6232,6 +6422,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6309,6 +6504,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6386,6 +6586,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6463,6 +6668,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6540,6 +6750,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6617,6 +6832,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6694,6 +6914,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6771,6 +6996,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6848,6 +7078,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6925,6 +7160,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7074,6 +7314,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7151,6 +7396,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7228,6 +7478,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7305,6 +7560,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9824,6 +10084,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9983,6 +10248,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10055,6 +10325,11 @@
           <t xml:space="preserve">25.06.26</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10440,6 +10715,11 @@
           <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10517,6 +10797,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10748,6 +11033,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10825,6 +11115,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10902,6 +11197,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10979,6 +11279,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11056,6 +11361,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11133,6 +11443,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11210,6 +11525,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11287,6 +11607,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11364,6 +11689,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11441,6 +11771,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11518,6 +11853,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11595,6 +11935,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11672,6 +12017,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11749,6 +12099,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12062,6 +12417,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12134,6 +12494,11 @@
           <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12365,6 +12730,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12442,6 +12812,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12519,6 +12894,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12591,6 +12971,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12914,6 +13299,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12991,6 +13381,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13314,6 +13709,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13555,6 +13955,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13679,6 +14084,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13721,6 +14131,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13763,6 +14178,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13805,6 +14225,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13847,6 +14272,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13889,6 +14319,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13931,6 +14366,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13973,6 +14413,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14015,6 +14460,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14057,6 +14507,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14099,6 +14554,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14141,6 +14601,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14183,6 +14648,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14225,6 +14695,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14267,6 +14742,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14309,6 +14789,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14351,6 +14836,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14393,6 +14883,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14435,6 +14930,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14477,6 +14977,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14519,6 +15024,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14561,6 +15071,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14603,6 +15118,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14645,6 +15165,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14687,6 +15212,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14729,6 +15259,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14771,6 +15306,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14813,6 +15353,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14855,6 +15400,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14897,6 +15447,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14939,6 +15494,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14981,6 +15541,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15023,6 +15588,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15065,6 +15635,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15107,6 +15682,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15149,6 +15729,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15191,6 +15776,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15233,6 +15823,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15275,6 +15870,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15317,6 +15917,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15359,6 +15964,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15401,6 +16011,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15443,6 +16058,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15485,6 +16105,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15527,6 +16152,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15569,6 +16199,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15611,6 +16246,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15653,6 +16293,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15695,6 +16340,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15737,6 +16387,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15779,6 +16434,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15821,6 +16481,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15863,6 +16528,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15905,6 +16575,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15947,6 +16622,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15989,6 +16669,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16031,6 +16716,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16073,6 +16763,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16115,6 +16810,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16157,6 +16857,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16199,6 +16904,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16241,6 +16951,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16283,6 +16998,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16325,6 +17045,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16367,6 +17092,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16409,6 +17139,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16451,6 +17186,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16493,6 +17233,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16535,6 +17280,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16577,6 +17327,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16619,6 +17374,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16661,6 +17421,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16703,6 +17468,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16745,6 +17515,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16787,6 +17562,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16829,6 +17609,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16871,6 +17656,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16913,6 +17703,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16955,6 +17750,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16997,6 +17797,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17039,6 +17844,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17081,6 +17891,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17123,6 +17938,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17165,6 +17985,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17207,6 +18032,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17249,6 +18079,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17291,6 +18126,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17333,6 +18173,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17375,6 +18220,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17417,6 +18267,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17459,6 +18314,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17501,6 +18361,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17543,6 +18408,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17585,6 +18455,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17627,6 +18502,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17669,6 +18549,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17711,6 +18596,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17753,6 +18643,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17795,6 +18690,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17837,6 +18737,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17879,6 +18784,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17921,6 +18831,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17963,6 +18878,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18005,6 +18925,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18047,6 +18972,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18089,6 +19019,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18131,6 +19066,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18173,6 +19113,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18215,6 +19160,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18257,6 +19207,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18299,6 +19254,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18341,6 +19301,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18383,6 +19348,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18425,6 +19395,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18467,6 +19442,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18509,6 +19489,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18551,6 +19536,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18593,6 +19583,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18635,6 +19630,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18677,6 +19677,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18719,6 +19724,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18761,6 +19771,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18803,6 +19818,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18845,6 +19865,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18887,6 +19912,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18929,6 +19959,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18971,6 +20006,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19013,6 +20053,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19055,6 +20100,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19097,6 +20147,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19139,6 +20194,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19181,6 +20241,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19223,6 +20288,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19265,6 +20335,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19307,6 +20382,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19349,6 +20429,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19391,6 +20476,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19433,6 +20523,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19475,6 +20570,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19517,6 +20617,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19559,6 +20664,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19601,6 +20711,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19643,6 +20758,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19685,6 +20805,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19727,6 +20852,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19769,6 +20899,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19811,6 +20946,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19853,6 +20993,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19895,6 +21040,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19937,6 +21087,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19979,6 +21134,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20021,6 +21181,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20063,6 +21228,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20105,6 +21275,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20147,6 +21322,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20189,6 +21369,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20231,6 +21416,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20273,6 +21463,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20315,6 +21510,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20357,6 +21557,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20399,6 +21604,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20441,6 +21651,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20483,6 +21698,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20525,6 +21745,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20567,6 +21792,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20609,6 +21839,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20651,6 +21886,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20693,6 +21933,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20735,6 +21980,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20777,6 +22027,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20819,6 +22074,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20861,6 +22121,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20903,6 +22168,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20945,6 +22215,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20987,6 +22262,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21029,6 +22309,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21071,6 +22356,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21113,6 +22403,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21155,6 +22450,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21197,6 +22497,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21239,6 +22544,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21281,6 +22591,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21323,6 +22638,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21365,6 +22685,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21407,6 +22732,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21449,6 +22779,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21491,6 +22826,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21533,6 +22873,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21575,6 +22920,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21617,6 +22967,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21659,6 +23014,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21701,6 +23061,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21743,6 +23108,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21785,6 +23155,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21827,6 +23202,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21869,6 +23249,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21911,6 +23296,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21953,6 +23343,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21995,6 +23390,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22037,6 +23437,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22079,6 +23484,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22121,6 +23531,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22163,6 +23578,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22205,6 +23625,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22247,6 +23672,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22289,6 +23719,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22331,6 +23766,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22373,6 +23813,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22415,6 +23860,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22457,6 +23907,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22499,6 +23954,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22541,6 +24001,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22583,6 +24048,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22625,6 +24095,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22667,6 +24142,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22709,6 +24189,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22751,6 +24236,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22793,6 +24283,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22835,6 +24330,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22877,6 +24377,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22919,6 +24424,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22961,6 +24471,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23003,6 +24518,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23045,6 +24565,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23087,6 +24612,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23129,6 +24659,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23171,6 +24706,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23213,6 +24753,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23255,6 +24800,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23297,6 +24847,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23339,6 +24894,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23381,6 +24941,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23423,6 +24988,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23465,6 +25035,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23507,6 +25082,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23549,6 +25129,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23591,6 +25176,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23633,6 +25223,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23675,6 +25270,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23717,6 +25317,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23759,6 +25364,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23801,6 +25411,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23843,6 +25458,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23885,6 +25505,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23927,6 +25552,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23969,6 +25599,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24011,6 +25646,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24053,6 +25693,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24095,6 +25740,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24137,6 +25787,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24179,6 +25834,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24221,6 +25881,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24263,6 +25928,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24305,6 +25975,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24347,6 +26022,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24389,6 +26069,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24431,6 +26116,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24473,6 +26163,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24515,6 +26210,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24557,6 +26257,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24599,6 +26304,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24641,6 +26351,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24683,6 +26398,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24725,6 +26445,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24767,6 +26492,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24809,6 +26539,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24851,6 +26586,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24893,6 +26633,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24935,6 +26680,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24977,6 +26727,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25019,6 +26774,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25061,6 +26821,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25103,6 +26868,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25145,6 +26915,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25187,6 +26962,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25229,6 +27009,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25271,6 +27056,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25313,6 +27103,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25355,6 +27150,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25397,6 +27197,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25439,6 +27244,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25481,6 +27291,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25523,6 +27338,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25565,6 +27385,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25607,6 +27432,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25649,6 +27479,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25691,6 +27526,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25733,6 +27573,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25775,6 +27620,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25817,6 +27667,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25859,6 +27714,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25901,6 +27761,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25943,6 +27808,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25985,6 +27855,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26027,6 +27902,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26069,6 +27949,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26111,6 +27996,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26153,6 +28043,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26195,6 +28090,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26237,6 +28137,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26279,6 +28184,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26321,6 +28231,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26363,6 +28278,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26405,6 +28325,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26447,6 +28372,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26489,6 +28419,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26531,6 +28466,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26573,6 +28513,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26615,6 +28560,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26657,6 +28607,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26699,6 +28654,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26741,6 +28701,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26783,6 +28748,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26825,6 +28795,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26867,6 +28842,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26909,6 +28889,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26951,6 +28936,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26993,6 +28983,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27035,6 +29030,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27077,6 +29077,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27119,6 +29124,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27161,6 +29171,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27203,6 +29218,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27245,6 +29265,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27287,6 +29312,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27329,6 +29359,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27371,6 +29406,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27413,6 +29453,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M504" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27455,6 +29500,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M505" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27497,6 +29547,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M506" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27537,6 +29592,11 @@
       <c r="J507" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -507,6 +507,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HN30</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -666,6 +671,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HN30</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -743,6 +753,11 @@
           <t xml:space="preserve">28.01.26</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HN30</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1223,6 +1238,11 @@
       <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HN30</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -355,7 +355,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -19840,7 +19840,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -20639,7 +20639,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -21485,7 +21485,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -21861,7 +21861,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -23882,7 +23882,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -24305,7 +24305,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -26279,7 +26279,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -26326,7 +26326,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -26420,7 +26420,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -26843,7 +26843,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -27125,7 +27125,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -27501,7 +27501,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -28300,7 +28300,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -28394,7 +28394,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -28488,7 +28488,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -28958,7 +28958,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
@@ -29146,7 +29146,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -29193,7 +29193,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -29240,7 +29240,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -29475,7 +29475,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -29616,7 +29616,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -206,7 +206,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -360,7 +360,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -437,7 +437,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16555,7 +16555,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -18999,7 +18999,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -19469,7 +19469,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -19892,7 +19892,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -21631,7 +21631,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -22195,7 +22195,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -22336,7 +22336,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -22477,7 +22477,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -22524,7 +22524,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -22712,7 +22712,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -22806,7 +22806,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -22853,7 +22853,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -23135,7 +23135,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -23511,7 +23511,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -24075,7 +24075,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -24545,7 +24545,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -24639,7 +24639,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -24874,7 +24874,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -24968,7 +24968,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -25250,7 +25250,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -25438,7 +25438,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -25579,7 +25579,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -25720,7 +25720,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -25814,7 +25814,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -26049,7 +26049,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -26143,7 +26143,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -26190,7 +26190,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -26425,7 +26425,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -26566,7 +26566,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -26895,7 +26895,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -27083,7 +27083,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -27177,7 +27177,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -27318,7 +27318,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -27365,7 +27365,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -27553,7 +27553,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -27835,7 +27835,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -27929,7 +27929,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -28023,7 +28023,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -28540,7 +28540,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -28869,7 +28869,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -29292,7 +29292,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
@@ -29433,7 +29433,7 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N505" t="inlineStr">
@@ -29574,7 +29574,7 @@
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N506" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
